--- a/data/MENDOZA COPPIANO ELICIO.xlsx
+++ b/data/MENDOZA COPPIANO ELICIO.xlsx
@@ -436,10 +436,10 @@
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
     <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -456,22 +456,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>marzo</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>marzo</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>mayo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>mayo</t>
+          <t>junio</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">

--- a/data/MENDOZA COPPIANO ELICIO.xlsx
+++ b/data/MENDOZA COPPIANO ELICIO.xlsx
@@ -437,8 +437,8 @@
     <col width="25" customWidth="1" min="1" max="1"/>
     <col width="33" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
@@ -456,22 +456,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>marzo</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>mayo</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>mayo</t>
+          <t>junio</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>junio</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">

--- a/data/MENDOZA COPPIANO ELICIO.xlsx
+++ b/data/MENDOZA COPPIANO ELICIO.xlsx
@@ -436,10 +436,10 @@
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
     <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -456,22 +456,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>mayo</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>mayo</t>
+          <t>junio</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>junio</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>agosto</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">

--- a/data/MENDOZA COPPIANO ELICIO.xlsx
+++ b/data/MENDOZA COPPIANO ELICIO.xlsx
@@ -436,10 +436,10 @@
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
     <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -456,22 +456,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>mayo</t>
+          <t>junio</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>junio</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>agosto</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>agosto</t>
+          <t>septiembre</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">

--- a/data/MENDOZA COPPIANO ELICIO.xlsx
+++ b/data/MENDOZA COPPIANO ELICIO.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="VENTA MENSUAL" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="VENTAS POR GRUPO" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -57,7 +58,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -65,6 +66,9 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -527,4 +531,272 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="26" customWidth="1" min="14" max="14"/>
+    <col width="17" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="17" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>CLIENTE</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>240X120 PORCELANATO</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>240X80 PORCELANATO</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>FREGADEROS DE COCINA</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>GRANITO</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>GRIFERIAS</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>INODOROS</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>LAVABOS</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>LED</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>PANELES DECORATIVOS</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>PIEDRA SINTERIZADA</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>PORCELANATO</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>PUERTAS DE SEGURIDAD</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>SAL SOLUBLE</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>NO RESURTIBLES</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>PANELES PVC</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>PANELES PU</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>MENDOZA COPPIANO ELICIO</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>MINUTOCORP S.A.</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>0 de 1</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>0 de 1</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>0 de 1</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>0 de 1</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>0 de 1</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>0 de 1</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>0 de 1</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>0 de 1</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>0 de 1</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>0 de 1</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>0 de 1</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>0 de 1</t>
+        </is>
+      </c>
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>0 de 1</t>
+        </is>
+      </c>
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>0 de 1</t>
+        </is>
+      </c>
+      <c r="Q3" s="4" t="inlineStr">
+        <is>
+          <t>0 de 1</t>
+        </is>
+      </c>
+      <c r="R3" s="4" t="inlineStr">
+        <is>
+          <t>0 de 1</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>